--- a/assessment_forms/021_ai_knowledge_assessment_quiz--assessment_forms.xlsx
+++ b/assessment_forms/021_ai_knowledge_assessment_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'hard-coding_every_possible_outcome_into_a_program.',_'value':_'wrong_1'}</t>
+          <t>hard-coding_every_possible_outcome_into_a_program.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Hard-coding every possible outcome into a program.', 'value': 'wrong_1'}</t>
+          <t>Hard-coding every possible outcome into a program.</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'a_subset_of_ai_that_allows_systems_to_learn_from_data_without_being_explicitly_programmed_for_every_task.',_'value':_'correct'}</t>
+          <t>a_subset_of_ai_that_allows_systems_to_learn_from_data_without_being_explicitly_programmed_for_every_task.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'A subset of AI that allows systems to learn from data without being explicitly programmed for every task.', 'value': 'correct'}</t>
+          <t>A subset of AI that allows systems to learn from data without being explicitly programmed for every task.</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'the_physical_construction_of_robotic_hardware.',_'value':_'wrong_2'}</t>
+          <t>the_physical_construction_of_robotic_hardware.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'The physical construction of robotic hardware.', 'value': 'wrong_2'}</t>
+          <t>The physical construction of robotic hardware.</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_"simple_automation_based_on_'if-then'_statements_only.",_'value':_'wrong_3'}</t>
+          <t>simple_automation_based_on_'if-then'_statements_only.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': "Simple automation based on 'if-then' statements only.", 'value': 'wrong_3'}</t>
+          <t>Simple automation based on 'if-then' statements only.</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cnn_(convolutional_neural_network)',_'value':_'cnn'}</t>
+          <t>cnn_(convolutional_neural_network)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'CNN (Convolutional Neural Network)', 'value': 'cnn'}</t>
+          <t>CNN (Convolutional Neural Network)</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'rnn_(recurrent_neural_network)',_'value':_'rnn'}</t>
+          <t>rnn_(recurrent_neural_network)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'RNN (Recurrent Neural Network)', 'value': 'rnn'}</t>
+          <t>RNN (Recurrent Neural Network)</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'decision_trees',_'value':_'decision_trees'}</t>
+          <t>decision_trees</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Decision Trees', 'value': 'decision_trees'}</t>
+          <t>Decision Trees</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'transformer',_'value':_'transformer'}</t>
+          <t>transformer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Transformer', 'value': 'transformer'}</t>
+          <t>Transformer</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'linear_regression',_'value':_'linear_reg'}</t>
+          <t>linear_regression</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Linear Regression', 'value': 'linear_reg'}</t>
+          <t>Linear Regression</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'the_model_is_too_simple_to_capture_the_underlying_patterns.',_'value':_'underfitting'}</t>
+          <t>the_model_is_too_simple_to_capture_the_underlying_patterns.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'The model is too simple to capture the underlying patterns.', 'value': 'underfitting'}</t>
+          <t>The model is too simple to capture the underlying patterns.</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'the_model_performs_well_on_training_data_but_poorly_on_new,_unseen_data.',_'value':_'overfitting'}</t>
+          <t>the_model_performs_well_on_training_data_but_poorly_on_new,_unseen_data.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'The model performs well on training data but poorly on new, unseen data.', 'value': 'overfitting'}</t>
+          <t>The model performs well on training data but poorly on new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'the_model_has_reached_perfect_accuracy_on_all_datasets.',_'value':_'perfect'}</t>
+          <t>the_model_has_reached_perfect_accuracy_on_all_datasets.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'The model has reached perfect accuracy on all datasets.', 'value': 'perfect'}</t>
+          <t>The model has reached perfect accuracy on all datasets.</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'gpt-4',_'value':_'gpt4'}</t>
+          <t>gpt-4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'GPT-4', 'value': 'gpt4'}</t>
+          <t>GPT-4</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'claude',_'value':_'claude'}</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Claude', 'value': 'claude'}</t>
+          <t>Claude</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'midjourney',_'value':_'midjourney'}</t>
+          <t>midjourney</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Midjourney', 'value': 'midjourney'}</t>
+          <t>Midjourney</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'sql_server',_'value':_'sql'}</t>
+          <t>sql_server</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'SQL Server', 'value': 'sql'}</t>
+          <t>SQL Server</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'stable_diffusion',_'value':_'stable_diff'}</t>
+          <t>stable_diffusion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Stable Diffusion', 'value': 'stable_diff'}</t>
+          <t>Stable Diffusion</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'flawed_or_unrepresentative_training_data.',_'value':_'correct'}</t>
+          <t>flawed_or_unrepresentative_training_data.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Flawed or unrepresentative training data.', 'value': 'correct'}</t>
+          <t>Flawed or unrepresentative training data.</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_"the_computer's_hardware_being_too_old.",_'value':_'hardware'}</t>
+          <t>the_computer's_hardware_being_too_old.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': "The computer's hardware being too old.", 'value': 'hardware'}</t>
+          <t>The computer's hardware being too old.</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'too_many_programmers_working_on_the_code.',_'value':_'staff'}</t>
+          <t>too_many_programmers_working_on_the_code.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Too many programmers working on the code.', 'value': 'staff'}</t>
+          <t>Too many programmers working on the code.</t>
         </is>
       </c>
     </row>
